--- a/data/sars/pacific/tables/Pacific_2007_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2007_Appendix3.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6451FD1A-AEA5-574E-8757-75E1CC6A8443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D2C070-07D6-DF43-9841-204FF875CA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="27100" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Table 1'!$A$1:$Q$63</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="102">
   <si>
     <t>California sea lion</t>
   </si>
@@ -397,13 +400,19 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>rf</t>
   </si>
   <si>
     <t>strategic_yn</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
   </si>
 </sst>
 </file>
@@ -876,11 +885,14 @@
     <col min="2" max="2" width="42.796875" style="2" customWidth="1"/>
     <col min="3" max="11" width="9.59765625" style="2" customWidth="1"/>
     <col min="12" max="12" width="13.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="21" width="9.59765625" style="2" customWidth="1"/>
+    <col min="13" max="15" width="9.59765625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="8.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="9.59765625" style="2" customWidth="1"/>
     <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
@@ -903,7 +915,7 @@
         <v>90</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>91</v>
@@ -915,7 +927,7 @@
         <v>93</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>94</v>
@@ -927,10 +939,13 @@
         <v>96</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+        <v>99</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -979,8 +994,11 @@
       <c r="P2" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q2" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1030,7 +1048,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1075,8 +1093,11 @@
       <c r="P4" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q4" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -1122,7 +1143,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1171,8 +1192,11 @@
       <c r="P6" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q6" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -1218,7 +1242,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>15</v>
       </c>
@@ -1268,7 +1292,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1317,8 +1341,11 @@
       <c r="P9" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q9" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
@@ -1368,7 +1395,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -1418,7 +1445,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>22</v>
       </c>
@@ -1468,7 +1495,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -1518,7 +1545,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -1568,7 +1595,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
@@ -1618,7 +1645,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>27</v>
       </c>
@@ -1667,8 +1694,11 @@
       <c r="P16" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q16" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>29</v>
       </c>
@@ -1717,8 +1747,11 @@
       <c r="P17" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q17" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>30</v>
       </c>
@@ -1767,8 +1800,11 @@
       <c r="P18" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q18" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>31</v>
       </c>
@@ -1818,7 +1854,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -1867,8 +1903,11 @@
       <c r="P20" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q20" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
@@ -1917,8 +1956,11 @@
       <c r="P21" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q21" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>35</v>
       </c>
@@ -1967,8 +2009,11 @@
       <c r="P22" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q22" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>36</v>
       </c>
@@ -2017,8 +2062,11 @@
       <c r="P23" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q23" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>37</v>
       </c>
@@ -2067,8 +2115,11 @@
       <c r="P24" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q24" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
@@ -2117,8 +2168,11 @@
       <c r="P25" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q25" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>38</v>
       </c>
@@ -2167,8 +2221,11 @@
       <c r="P26" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q26" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>42</v>
       </c>
@@ -2217,8 +2274,11 @@
       <c r="P27" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q27" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -2267,8 +2327,11 @@
       <c r="P28" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q28" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>44</v>
       </c>
@@ -2317,8 +2380,11 @@
       <c r="P29" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q29" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>45</v>
       </c>
@@ -2367,8 +2433,11 @@
       <c r="P30" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q30" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>47</v>
       </c>
@@ -2417,8 +2486,11 @@
       <c r="P31" s="8">
         <v>2007</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q31" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>48</v>
       </c>
@@ -2466,6 +2538,9 @@
       </c>
       <c r="P32" s="8">
         <v>2007</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.15">
@@ -2517,6 +2592,9 @@
       <c r="P33" s="8">
         <v>2007</v>
       </c>
+      <c r="Q33" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
@@ -2567,6 +2645,9 @@
       <c r="P34" s="8">
         <v>2007</v>
       </c>
+      <c r="Q34" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="35" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
@@ -2617,6 +2698,9 @@
       <c r="P35" s="8">
         <v>2007</v>
       </c>
+      <c r="Q35" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="36" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
@@ -2667,6 +2751,9 @@
       <c r="P36" s="8">
         <v>2007</v>
       </c>
+      <c r="Q36" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="37" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
@@ -2717,6 +2804,9 @@
       <c r="P37" s="8">
         <v>2007</v>
       </c>
+      <c r="Q37" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
@@ -2767,6 +2857,9 @@
       <c r="P38" s="8">
         <v>2007</v>
       </c>
+      <c r="Q38" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="39" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
@@ -2817,6 +2910,9 @@
       <c r="P39" s="8">
         <v>2007</v>
       </c>
+      <c r="Q39" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="40" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
@@ -3276,7 +3372,9 @@
       <c r="P49" s="8">
         <v>2007</v>
       </c>
-      <c r="Q49" s="3"/>
+      <c r="Q49" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="50" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="4" t="s">
@@ -3322,7 +3420,9 @@
       <c r="P50" s="8">
         <v>2007</v>
       </c>
-      <c r="Q50" s="1"/>
+      <c r="Q50" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="51" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="s">
@@ -3919,6 +4019,7 @@
       <c r="Q63" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Q63" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
